--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716552.3096640431</v>
+        <v>716552</v>
       </c>
       <c r="R2" t="n">
-        <v>6352177.930767611</v>
+        <v>6352178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1991-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>101731</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716572.3713152856</v>
+        <v>716572</v>
       </c>
       <c r="R3" t="n">
-        <v>6352178.447933715</v>
+        <v>6352178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>1991-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107224</v>
+        <v>107233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104080</v>
+        <v>104089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107233</v>
+        <v>107245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104089</v>
+        <v>104101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104101</v>
+        <v>104110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104110</v>
+        <v>104113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104113</v>
+        <v>104140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104140</v>
+        <v>104146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104146</v>
+        <v>104153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104153</v>
+        <v>104157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104157</v>
+        <v>104164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104167</v>
+        <v>104172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106394717</v>
       </c>
       <c r="B2" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106394719</v>
       </c>
       <c r="B3" t="n">
-        <v>104172</v>
+        <v>104180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106394717</v>
+        <v>106394719</v>
       </c>
       <c r="B2" t="n">
-        <v>107328</v>
+        <v>104681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alvare drygt 900 m N, Gtl</t>
+          <t>Alvare 900 m N, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716552</v>
+        <v>716572</v>
       </c>
       <c r="R2" t="n">
         <v>6352178</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106394719</v>
+        <v>106394724</v>
       </c>
       <c r="B3" t="n">
-        <v>104180</v>
+        <v>104681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,14 +812,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alvare 900 m N, Gtl</t>
+          <t>Alvare 650 m N, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716572</v>
+        <v>716786</v>
       </c>
       <c r="R3" t="n">
-        <v>6352178</v>
+        <v>6351921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +880,218 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106394717</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107868</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1855</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Åkerkulla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anthemis arvensis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alvare drygt 900 m N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>716552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6352178</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1991-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1991-07-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventeringsläger i GBF:s regi.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingrid Engqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106394723</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107868</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1855</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Åkerkulla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anthemis arvensis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alvare 650 m N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>716786</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6351921</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1991-07-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1991-07-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventeringsläger i GBF:s regi.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ingrid Engqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 28276-2024 artfynd.xlsx
+++ b/artfynd/A 28276-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106394719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106394724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106394717</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106394723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>